--- a/excel_routes/route_CAI_ELQ_threats.xlsx
+++ b/excel_routes/route_CAI_ELQ_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881ED8C4-FC83-4B47-88B2-FB48AB189783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5DA482-83E1-4ACE-BB23-9C27B6ED9C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="50">
   <si>
     <t>Date</t>
   </si>
@@ -81,21 +81,30 @@
     <t>31-JUL-26</t>
   </si>
   <si>
+    <t>Nile Air NP-115</t>
+  </si>
+  <si>
+    <t>04-AUG-26</t>
+  </si>
+  <si>
+    <t>05-AUG-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-315</t>
+  </si>
+  <si>
+    <t>07-AUG-26</t>
+  </si>
+  <si>
+    <t>11-AUG-26</t>
+  </si>
+  <si>
+    <t>12-AUG-26</t>
+  </si>
+  <si>
     <t>Air Arabia Egypt E5-591</t>
   </si>
   <si>
-    <t>Nile Air NP-115</t>
-  </si>
-  <si>
-    <t>04-AUG-26</t>
-  </si>
-  <si>
-    <t>05-AUG-26</t>
-  </si>
-  <si>
-    <t>07-AUG-26</t>
-  </si>
-  <si>
     <t>14-AUG-26</t>
   </si>
   <si>
@@ -106,9 +115,6 @@
   </si>
   <si>
     <t>MED</t>
-  </si>
-  <si>
-    <t>Nile Air NP-315</t>
   </si>
   <si>
     <t>21-AUG-26</t>
@@ -565,7 +571,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -626,13 +632,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>14758</v>
+        <v>15208</v>
       </c>
       <c r="E2" s="2">
-        <v>16833</v>
+        <v>16832</v>
       </c>
       <c r="F2" s="2">
-        <v>-2075</v>
+        <v>-1624</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -664,10 +670,10 @@
         <v>15208</v>
       </c>
       <c r="E3" s="2">
-        <v>16833</v>
+        <v>16832</v>
       </c>
       <c r="F3" s="2">
-        <v>-1625</v>
+        <v>-1624</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
@@ -696,22 +702,22 @@
         <v>18</v>
       </c>
       <c r="D4" s="2">
-        <v>14101</v>
+        <v>15208</v>
       </c>
       <c r="E4" s="2">
-        <v>16833</v>
+        <v>16832</v>
       </c>
       <c r="F4" s="2">
-        <v>-2732</v>
+        <v>-1624</v>
       </c>
       <c r="G4" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2">
         <v>30</v>
       </c>
       <c r="I4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>14</v>
@@ -731,13 +737,13 @@
         <v>16</v>
       </c>
       <c r="D5" s="2">
-        <v>15208</v>
+        <v>16628</v>
       </c>
       <c r="E5" s="2">
-        <v>16833</v>
+        <v>16832</v>
       </c>
       <c r="F5" s="2">
-        <v>-1625</v>
+        <v>-204</v>
       </c>
       <c r="G5" s="2">
         <v>30</v>
@@ -757,22 +763,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2">
-        <v>15208</v>
+        <v>10648</v>
       </c>
       <c r="E6" s="2">
-        <v>16833</v>
+        <v>11849</v>
       </c>
       <c r="F6" s="2">
-        <v>-1625</v>
+        <v>-1201</v>
       </c>
       <c r="G6" s="2">
         <v>30</v>
@@ -798,16 +804,16 @@
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2">
-        <v>10607</v>
+        <v>10648</v>
       </c>
       <c r="E7" s="2">
         <v>10853</v>
       </c>
       <c r="F7" s="2">
-        <v>-246</v>
+        <v>-205</v>
       </c>
       <c r="G7" s="2">
         <v>30</v>
@@ -827,13 +833,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2">
         <v>10648</v>
@@ -862,22 +868,22 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
-        <v>10607</v>
+        <v>10648</v>
       </c>
       <c r="E9" s="2">
-        <v>10853</v>
+        <v>11849</v>
       </c>
       <c r="F9" s="2">
-        <v>-246</v>
+        <v>-1201</v>
       </c>
       <c r="G9" s="2">
         <v>30</v>
@@ -897,31 +903,31 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2">
-        <v>10648</v>
+        <v>10597</v>
       </c>
       <c r="E10" s="2">
-        <v>10853</v>
+        <v>13338</v>
       </c>
       <c r="F10" s="2">
-        <v>-205</v>
+        <v>-2741</v>
       </c>
       <c r="G10" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2">
         <v>30</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>14</v>
@@ -932,22 +938,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2">
         <v>10648</v>
       </c>
       <c r="E11" s="2">
-        <v>10853</v>
+        <v>13338</v>
       </c>
       <c r="F11" s="2">
-        <v>-205</v>
+        <v>-2690</v>
       </c>
       <c r="G11" s="2">
         <v>30</v>
@@ -967,31 +973,31 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2">
-        <v>13276</v>
+        <v>10648</v>
       </c>
       <c r="E12" s="2">
-        <v>14840</v>
+        <v>13338</v>
       </c>
       <c r="F12" s="2">
-        <v>-1564</v>
+        <v>-2690</v>
       </c>
       <c r="G12" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>14</v>
@@ -1011,10 +1017,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="2">
-        <v>13392</v>
+        <v>11890</v>
       </c>
       <c r="E13" s="2">
-        <v>14840</v>
+        <v>13338</v>
       </c>
       <c r="F13" s="2">
         <v>-1448</v>
@@ -1037,31 +1043,31 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2">
-        <v>13502</v>
+        <v>13223</v>
       </c>
       <c r="E14" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F14" s="2">
-        <v>-1338</v>
+        <v>-1616</v>
       </c>
       <c r="G14" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2">
         <v>30</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>14</v>
@@ -1072,19 +1078,19 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2">
-        <v>13502</v>
+        <v>13501</v>
       </c>
       <c r="E15" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F15" s="2">
         <v>-1338</v>
@@ -1107,22 +1113,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2">
-        <v>11891</v>
+        <v>13501</v>
       </c>
       <c r="E16" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F16" s="2">
-        <v>-2949</v>
+        <v>-1338</v>
       </c>
       <c r="G16" s="2">
         <v>30</v>
@@ -1133,8 +1139,8 @@
       <c r="I16" s="2">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>26</v>
+      <c r="J16" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>15</v>
@@ -1142,31 +1148,31 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2">
-        <v>12176</v>
+        <v>13392</v>
       </c>
       <c r="E17" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F17" s="2">
-        <v>-2664</v>
+        <v>-1447</v>
       </c>
       <c r="G17" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2">
         <v>30</v>
       </c>
       <c r="I17" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>14</v>
@@ -1177,7 +1183,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1186,10 +1192,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="2">
-        <v>13502</v>
+        <v>13501</v>
       </c>
       <c r="E18" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F18" s="2">
         <v>-1338</v>
@@ -1212,19 +1218,19 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D19" s="2">
-        <v>13502</v>
+        <v>13501</v>
       </c>
       <c r="E19" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F19" s="2">
         <v>-1338</v>
@@ -1253,28 +1259,28 @@
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D20" s="2">
-        <v>12764</v>
+        <v>12000</v>
       </c>
       <c r="E20" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F20" s="2">
-        <v>-2076</v>
+        <v>-2839</v>
       </c>
       <c r="G20" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2">
         <v>30</v>
       </c>
       <c r="I20" s="2">
-        <v>10</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1288,25 +1294,25 @@
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D21" s="2">
-        <v>13502</v>
+        <v>12127</v>
       </c>
       <c r="E21" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F21" s="2">
-        <v>-1338</v>
+        <v>-2712</v>
       </c>
       <c r="G21" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2">
         <v>30</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>14</v>
@@ -1323,16 +1329,16 @@
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D22" s="2">
-        <v>13502</v>
+        <v>13392</v>
       </c>
       <c r="E22" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F22" s="2">
-        <v>-1338</v>
+        <v>-1447</v>
       </c>
       <c r="G22" s="2">
         <v>30</v>
@@ -1352,31 +1358,31 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2">
-        <v>11659</v>
+        <v>13501</v>
       </c>
       <c r="E23" s="2">
-        <v>11850</v>
+        <v>14839</v>
       </c>
       <c r="F23" s="2">
-        <v>-191</v>
+        <v>-1338</v>
       </c>
       <c r="G23" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2">
         <v>30</v>
       </c>
       <c r="I23" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>14</v>
@@ -1387,31 +1393,31 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D24" s="2">
-        <v>10225</v>
+        <v>13223</v>
       </c>
       <c r="E24" s="2">
-        <v>11850</v>
+        <v>14839</v>
       </c>
       <c r="F24" s="2">
-        <v>-1625</v>
+        <v>-1616</v>
       </c>
       <c r="G24" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H24" s="2">
         <v>30</v>
       </c>
       <c r="I24" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>14</v>
@@ -1422,31 +1428,31 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D25" s="2">
-        <v>10717</v>
+        <v>13501</v>
       </c>
       <c r="E25" s="2">
-        <v>13338</v>
+        <v>14839</v>
       </c>
       <c r="F25" s="2">
-        <v>-2621</v>
+        <v>-1338</v>
       </c>
       <c r="G25" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2">
         <v>30</v>
       </c>
       <c r="I25" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>14</v>
@@ -1457,22 +1463,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D26" s="2">
-        <v>10853</v>
+        <v>13501</v>
       </c>
       <c r="E26" s="2">
-        <v>13338</v>
+        <v>14839</v>
       </c>
       <c r="F26" s="2">
-        <v>-2485</v>
+        <v>-1338</v>
       </c>
       <c r="G26" s="2">
         <v>30</v>
@@ -1492,31 +1498,31 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="D27" s="2">
-        <v>10853</v>
+        <v>11658</v>
       </c>
       <c r="E27" s="2">
-        <v>13338</v>
+        <v>11849</v>
       </c>
       <c r="F27" s="2">
-        <v>-2485</v>
+        <v>-191</v>
       </c>
       <c r="G27" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2">
         <v>30</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>14</v>
@@ -1527,34 +1533,34 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="D28" s="2">
-        <v>11659</v>
+        <v>10225</v>
       </c>
       <c r="E28" s="2">
-        <v>13338</v>
+        <v>11849</v>
       </c>
       <c r="F28" s="2">
-        <v>-1679</v>
+        <v>-1624</v>
       </c>
       <c r="G28" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2">
         <v>30</v>
       </c>
       <c r="I28" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>15</v>
@@ -1568,28 +1574,28 @@
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D29" s="2">
-        <v>10334</v>
+        <v>10648</v>
       </c>
       <c r="E29" s="2">
-        <v>13338</v>
+        <v>11849</v>
       </c>
       <c r="F29" s="2">
-        <v>-3004</v>
+        <v>-1201</v>
       </c>
       <c r="G29" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2">
         <v>30</v>
       </c>
       <c r="I29" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>15</v>
@@ -1603,16 +1609,16 @@
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D30" s="2">
-        <v>10607</v>
+        <v>10648</v>
       </c>
       <c r="E30" s="2">
-        <v>13338</v>
+        <v>11849</v>
       </c>
       <c r="F30" s="2">
-        <v>-2731</v>
+        <v>-1201</v>
       </c>
       <c r="G30" s="2">
         <v>30</v>
@@ -1623,8 +1629,8 @@
       <c r="I30" s="2">
         <v>0</v>
       </c>
-      <c r="J30" s="4" t="s">
-        <v>26</v>
+      <c r="J30" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>15</v>
@@ -1632,31 +1638,31 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D31" s="2">
-        <v>11863</v>
+        <v>10674</v>
       </c>
       <c r="E31" s="2">
         <v>13338</v>
       </c>
       <c r="F31" s="2">
-        <v>-1475</v>
+        <v>-2664</v>
       </c>
       <c r="G31" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2">
         <v>30</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>14</v>
@@ -1673,28 +1679,28 @@
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D32" s="2">
-        <v>8341</v>
+        <v>12000</v>
       </c>
       <c r="E32" s="2">
         <v>13338</v>
       </c>
       <c r="F32" s="2">
-        <v>-4997</v>
+        <v>-1338</v>
       </c>
       <c r="G32" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2">
         <v>30</v>
       </c>
       <c r="I32" s="2">
-        <v>10</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>15</v>
@@ -1708,25 +1714,25 @@
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D33" s="2">
-        <v>10225</v>
+        <v>12000</v>
       </c>
       <c r="E33" s="2">
         <v>13338</v>
       </c>
       <c r="F33" s="2">
-        <v>-3113</v>
+        <v>-1338</v>
       </c>
       <c r="G33" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2">
         <v>30</v>
       </c>
       <c r="I33" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>14</v>
@@ -1743,28 +1749,28 @@
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D34" s="2">
-        <v>10607</v>
+        <v>12737</v>
       </c>
       <c r="E34" s="2">
         <v>13338</v>
       </c>
       <c r="F34" s="2">
-        <v>-2731</v>
+        <v>-601</v>
       </c>
       <c r="G34" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2">
         <v>30</v>
       </c>
       <c r="I34" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>15</v>
@@ -1772,34 +1778,34 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D35" s="2">
-        <v>11863</v>
+        <v>10580</v>
       </c>
       <c r="E35" s="2">
         <v>13338</v>
       </c>
       <c r="F35" s="2">
-        <v>-1475</v>
+        <v>-2758</v>
       </c>
       <c r="G35" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2">
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1813,28 +1819,28 @@
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D36" s="2">
-        <v>8925</v>
+        <v>10607</v>
       </c>
       <c r="E36" s="2">
         <v>13338</v>
       </c>
       <c r="F36" s="2">
-        <v>-4413</v>
+        <v>-2731</v>
       </c>
       <c r="G36" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2">
         <v>30</v>
       </c>
       <c r="I36" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>15</v>
@@ -1842,34 +1848,34 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D37" s="2">
-        <v>10334</v>
+        <v>8813</v>
       </c>
       <c r="E37" s="2">
         <v>13338</v>
       </c>
       <c r="F37" s="2">
-        <v>-3004</v>
+        <v>-4525</v>
       </c>
       <c r="G37" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2">
         <v>30</v>
       </c>
       <c r="I37" s="2">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>15</v>
@@ -1877,22 +1883,22 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D38" s="2">
-        <v>10853</v>
+        <v>9870</v>
       </c>
       <c r="E38" s="2">
         <v>13338</v>
       </c>
       <c r="F38" s="2">
-        <v>-2485</v>
+        <v>-3468</v>
       </c>
       <c r="G38" s="2">
         <v>30</v>
@@ -1903,8 +1909,8 @@
       <c r="I38" s="2">
         <v>0</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>14</v>
+      <c r="J38" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>15</v>
@@ -1912,31 +1918,31 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D39" s="2">
-        <v>10853</v>
+        <v>10225</v>
       </c>
       <c r="E39" s="2">
         <v>13338</v>
       </c>
       <c r="F39" s="2">
-        <v>-2485</v>
+        <v>-3113</v>
       </c>
       <c r="G39" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H39" s="2">
         <v>30</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>14</v>
@@ -1947,34 +1953,34 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D40" s="2">
-        <v>8914</v>
+        <v>8889</v>
       </c>
       <c r="E40" s="2">
         <v>13338</v>
       </c>
       <c r="F40" s="2">
-        <v>-4424</v>
+        <v>-4449</v>
       </c>
       <c r="G40" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2">
         <v>30</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>15</v>
@@ -1982,34 +1988,34 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D41" s="2">
-        <v>10130</v>
+        <v>10334</v>
       </c>
       <c r="E41" s="2">
         <v>13338</v>
       </c>
       <c r="F41" s="2">
-        <v>-3208</v>
+        <v>-3004</v>
       </c>
       <c r="G41" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2">
         <v>30</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>15</v>
@@ -2017,31 +2023,31 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D42" s="2">
-        <v>10225</v>
+        <v>12000</v>
       </c>
       <c r="E42" s="2">
         <v>13338</v>
       </c>
       <c r="F42" s="2">
-        <v>-3113</v>
+        <v>-1338</v>
       </c>
       <c r="G42" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2">
         <v>30</v>
       </c>
       <c r="I42" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>14</v>
@@ -2061,25 +2067,25 @@
         <v>18</v>
       </c>
       <c r="D43" s="2">
-        <v>8336</v>
+        <v>12000</v>
       </c>
       <c r="E43" s="2">
         <v>13338</v>
       </c>
       <c r="F43" s="2">
-        <v>-5002</v>
+        <v>-1338</v>
       </c>
       <c r="G43" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2">
         <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>10</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>15</v>
@@ -2087,7 +2093,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>12</v>
@@ -2114,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>15</v>
@@ -2122,34 +2128,34 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D45" s="2">
-        <v>10130</v>
+        <v>10225</v>
       </c>
       <c r="E45" s="2">
         <v>13338</v>
       </c>
       <c r="F45" s="2">
-        <v>-3208</v>
+        <v>-3113</v>
       </c>
       <c r="G45" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H45" s="2">
         <v>30</v>
       </c>
       <c r="I45" s="2">
-        <v>0</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>15</v>
@@ -2157,31 +2163,31 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D46" s="2">
-        <v>10225</v>
+        <v>10648</v>
       </c>
       <c r="E46" s="2">
         <v>13338</v>
       </c>
       <c r="F46" s="2">
-        <v>-3113</v>
+        <v>-2690</v>
       </c>
       <c r="G46" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2">
         <v>30</v>
       </c>
       <c r="I46" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>14</v>
@@ -2192,22 +2198,22 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D47" s="2">
-        <v>8413</v>
+        <v>8303</v>
       </c>
       <c r="E47" s="2">
         <v>13338</v>
       </c>
       <c r="F47" s="2">
-        <v>-4925</v>
+        <v>-5035</v>
       </c>
       <c r="G47" s="2">
         <v>20</v>
@@ -2219,7 +2225,7 @@
         <v>10</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>15</v>
@@ -2227,22 +2233,22 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D48" s="2">
-        <v>10130</v>
+        <v>8914</v>
       </c>
       <c r="E48" s="2">
         <v>13338</v>
       </c>
       <c r="F48" s="2">
-        <v>-3208</v>
+        <v>-4424</v>
       </c>
       <c r="G48" s="2">
         <v>30</v>
@@ -2254,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>15</v>
@@ -2262,34 +2268,34 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D49" s="2">
-        <v>10130</v>
+        <v>10225</v>
       </c>
       <c r="E49" s="2">
         <v>13338</v>
       </c>
       <c r="F49" s="2">
-        <v>-3208</v>
+        <v>-3113</v>
       </c>
       <c r="G49" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H49" s="2">
         <v>30</v>
       </c>
       <c r="I49" s="2">
-        <v>0</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>15</v>
@@ -2297,31 +2303,31 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D50" s="2">
-        <v>10225</v>
+        <v>10648</v>
       </c>
       <c r="E50" s="2">
         <v>13338</v>
       </c>
       <c r="F50" s="2">
-        <v>-3113</v>
+        <v>-2690</v>
       </c>
       <c r="G50" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2">
         <v>30</v>
       </c>
       <c r="I50" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>14</v>
@@ -2332,34 +2338,34 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D51" s="2">
-        <v>8600</v>
+        <v>8380</v>
       </c>
       <c r="E51" s="2">
         <v>13338</v>
       </c>
       <c r="F51" s="2">
-        <v>-4738</v>
+        <v>-4958</v>
       </c>
       <c r="G51" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2">
         <v>30</v>
       </c>
       <c r="I51" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>15</v>
@@ -2367,34 +2373,34 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D52" s="2">
-        <v>9392</v>
+        <v>10225</v>
       </c>
       <c r="E52" s="2">
         <v>13338</v>
       </c>
       <c r="F52" s="2">
-        <v>-3946</v>
+        <v>-3113</v>
       </c>
       <c r="G52" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H52" s="2">
         <v>30</v>
       </c>
       <c r="I52" s="2">
-        <v>0</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>15</v>
@@ -2402,31 +2408,31 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D53" s="2">
-        <v>10225</v>
+        <v>10648</v>
       </c>
       <c r="E53" s="2">
         <v>13338</v>
       </c>
       <c r="F53" s="2">
-        <v>-3113</v>
+        <v>-2690</v>
       </c>
       <c r="G53" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2">
         <v>30</v>
       </c>
       <c r="I53" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>14</v>
@@ -2446,25 +2452,25 @@
         <v>18</v>
       </c>
       <c r="D54" s="2">
-        <v>7568</v>
+        <v>10648</v>
       </c>
       <c r="E54" s="2">
         <v>13338</v>
       </c>
       <c r="F54" s="2">
-        <v>-5770</v>
+        <v>-2690</v>
       </c>
       <c r="G54" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H54" s="2">
         <v>30</v>
       </c>
       <c r="I54" s="2">
-        <v>10</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>15</v>
@@ -2472,34 +2478,34 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D55" s="2">
-        <v>7631</v>
+        <v>8600</v>
       </c>
       <c r="E55" s="2">
         <v>13338</v>
       </c>
       <c r="F55" s="2">
-        <v>-5707</v>
+        <v>-4738</v>
       </c>
       <c r="G55" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H55" s="2">
         <v>30</v>
       </c>
       <c r="I55" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>15</v>
@@ -2507,22 +2513,22 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D56" s="2">
-        <v>8314</v>
+        <v>9911</v>
       </c>
       <c r="E56" s="2">
         <v>13338</v>
       </c>
       <c r="F56" s="2">
-        <v>-5024</v>
+        <v>-3427</v>
       </c>
       <c r="G56" s="2">
         <v>30</v>
@@ -2534,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>15</v>
@@ -2542,34 +2548,34 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D57" s="2">
-        <v>10130</v>
+        <v>10225</v>
       </c>
       <c r="E57" s="2">
         <v>13338</v>
       </c>
       <c r="F57" s="2">
-        <v>-3208</v>
+        <v>-3113</v>
       </c>
       <c r="G57" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H57" s="2">
         <v>30</v>
       </c>
       <c r="I57" s="2">
-        <v>0</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>15</v>
@@ -2577,34 +2583,34 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D58" s="2">
-        <v>7631</v>
+        <v>7538</v>
       </c>
       <c r="E58" s="2">
         <v>13338</v>
       </c>
       <c r="F58" s="2">
-        <v>-5707</v>
+        <v>-5800</v>
       </c>
       <c r="G58" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2">
         <v>30</v>
       </c>
       <c r="I58" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>15</v>
@@ -2612,34 +2618,34 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D59" s="2">
-        <v>7645</v>
+        <v>7631</v>
       </c>
       <c r="E59" s="2">
         <v>13338</v>
       </c>
       <c r="F59" s="2">
-        <v>-5693</v>
+        <v>-5707</v>
       </c>
       <c r="G59" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H59" s="2">
         <v>30</v>
       </c>
       <c r="I59" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>15</v>
@@ -2647,22 +2653,22 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D60" s="2">
-        <v>9392</v>
+        <v>8314</v>
       </c>
       <c r="E60" s="2">
         <v>13338</v>
       </c>
       <c r="F60" s="2">
-        <v>-3946</v>
+        <v>-5024</v>
       </c>
       <c r="G60" s="2">
         <v>30</v>
@@ -2674,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>15</v>
@@ -2682,22 +2688,22 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D61" s="2">
-        <v>9392</v>
+        <v>10648</v>
       </c>
       <c r="E61" s="2">
         <v>13338</v>
       </c>
       <c r="F61" s="2">
-        <v>-3946</v>
+        <v>-2690</v>
       </c>
       <c r="G61" s="2">
         <v>30</v>
@@ -2708,8 +2714,8 @@
       <c r="I61" s="2">
         <v>0</v>
       </c>
-      <c r="J61" s="4" t="s">
-        <v>26</v>
+      <c r="J61" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>15</v>
@@ -2717,34 +2723,34 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D62" s="2">
-        <v>8314</v>
+        <v>7615</v>
       </c>
       <c r="E62" s="2">
-        <v>8355</v>
+        <v>13338</v>
       </c>
       <c r="F62" s="2">
-        <v>-41</v>
+        <v>-5723</v>
       </c>
       <c r="G62" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H62" s="2">
         <v>30</v>
       </c>
       <c r="I62" s="2">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>15</v>
@@ -2758,28 +2764,28 @@
         <v>12</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D63" s="2">
-        <v>8314</v>
+        <v>7631</v>
       </c>
       <c r="E63" s="2">
-        <v>8355</v>
+        <v>13338</v>
       </c>
       <c r="F63" s="2">
-        <v>-41</v>
+        <v>-5707</v>
       </c>
       <c r="G63" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H63" s="2">
         <v>30</v>
       </c>
       <c r="I63" s="2">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>15</v>
@@ -2787,34 +2793,34 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D64" s="2">
-        <v>7631</v>
+        <v>9911</v>
       </c>
       <c r="E64" s="2">
-        <v>8860</v>
+        <v>13338</v>
       </c>
       <c r="F64" s="2">
-        <v>-1229</v>
+        <v>-3427</v>
       </c>
       <c r="G64" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H64" s="2">
         <v>30</v>
       </c>
       <c r="I64" s="2">
-        <v>7</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>15</v>
@@ -2822,22 +2828,22 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D65" s="2">
-        <v>8314</v>
+        <v>9911</v>
       </c>
       <c r="E65" s="2">
-        <v>8355</v>
+        <v>13338</v>
       </c>
       <c r="F65" s="2">
-        <v>-41</v>
+        <v>-3427</v>
       </c>
       <c r="G65" s="2">
         <v>30</v>
@@ -2848,8 +2854,8 @@
       <c r="I65" s="2">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>14</v>
+      <c r="J65" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>15</v>
@@ -2857,7 +2863,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>12</v>
@@ -2892,31 +2898,31 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D67" s="2">
-        <v>7568</v>
+        <v>8314</v>
       </c>
       <c r="E67" s="2">
-        <v>9351</v>
+        <v>8355</v>
       </c>
       <c r="F67" s="2">
-        <v>-1783</v>
+        <v>-41</v>
       </c>
       <c r="G67" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H67" s="2">
         <v>30</v>
       </c>
       <c r="I67" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>14</v>
@@ -2927,36 +2933,176 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" s="2">
+        <v>7631</v>
+      </c>
+      <c r="E68" s="2">
+        <v>8860</v>
+      </c>
+      <c r="F68" s="2">
+        <v>-1229</v>
+      </c>
+      <c r="G68" s="2">
+        <v>23</v>
+      </c>
+      <c r="H68" s="2">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2">
+        <v>7</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D68" s="2">
+      <c r="B69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="2">
+        <v>8314</v>
+      </c>
+      <c r="E69" s="2">
+        <v>8355</v>
+      </c>
+      <c r="F69" s="2">
+        <v>-41</v>
+      </c>
+      <c r="G69" s="2">
+        <v>30</v>
+      </c>
+      <c r="H69" s="2">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="2">
+        <v>8314</v>
+      </c>
+      <c r="E70" s="2">
+        <v>8355</v>
+      </c>
+      <c r="F70" s="2">
+        <v>-41</v>
+      </c>
+      <c r="G70" s="2">
+        <v>30</v>
+      </c>
+      <c r="H70" s="2">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" s="2">
+        <v>7538</v>
+      </c>
+      <c r="E71" s="2">
+        <v>9351</v>
+      </c>
+      <c r="F71" s="2">
+        <v>-1813</v>
+      </c>
+      <c r="G71" s="2">
+        <v>20</v>
+      </c>
+      <c r="H71" s="2">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2">
+        <v>10</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" s="2">
         <v>8286</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E72" s="2">
         <v>9351</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F72" s="2">
         <v>-1065</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G72" s="2">
         <v>46</v>
       </c>
-      <c r="H68" s="2">
-        <v>30</v>
-      </c>
-      <c r="I68" s="2">
+      <c r="H72" s="2">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2">
         <v>-16</v>
       </c>
-      <c r="J68" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K68" s="2" t="s">
+      <c r="J72" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K72" s="2" t="s">
         <v>15</v>
       </c>
     </row>
